--- a/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92535490546</v>
+        <v>46157.93108713334</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108713334</v>
+        <v>46157.93364802253</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93364802253</v>
+        <v>46157.93665749129</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93665749129</v>
+        <v>46158.28191383003</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28191383003</v>
+        <v>46158.29710023481</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29710023481</v>
+        <v>46158.29785742007</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29785742007</v>
+        <v>46158.33352413833</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33352413833</v>
+        <v>46158.37208905572</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.5_Госпошлина/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37208905572</v>
+        <v>46158.37425350766</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
